--- a/Assets/MasterData/ExcelFiles/testScenario.xlsx
+++ b/Assets/MasterData/ExcelFiles/testScenario.xlsx
@@ -5,42 +5,328 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OGIX-PC046\source\repos\Unity6Test\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OGIX-PC046\source\repos\Unity6Test\Assets\MasterData\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{653A5C3B-203C-4DC4-8494-17A73DEB5EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D4D22B-5C11-4213-9B5D-B09AD4D05F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="1050" windowWidth="25620" windowHeight="14385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ADV_Texture" sheetId="1" r:id="rId1"/>
-    <sheet name="ADV_Scenario" sheetId="2" r:id="rId2"/>
+    <sheet name="#guide" sheetId="5" r:id="rId1"/>
+    <sheet name="ADV_Layer" sheetId="4" r:id="rId2"/>
     <sheet name="ADV_Character" sheetId="3" r:id="rId3"/>
+    <sheet name="ADV_Texture" sheetId="1" r:id="rId4"/>
+    <sheet name="ADV_ScenarioLabel" sheetId="6" r:id="rId5"/>
+    <sheet name="ADV_Scenario" sheetId="2" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="65">
   <si>
     <t>Command</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Arg1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Arg2</t>
-  </si>
-  <si>
-    <t>Arg3</t>
+    <t>x</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>order</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>spriteName</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>width</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>height</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>characterId</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>imageName</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>textureType</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>size</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中央</t>
+    <rPh sb="0" eb="2">
+      <t>チュウオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左</t>
+    <rPh sb="0" eb="1">
+      <t>ヒダリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右</t>
+    <rPh sb="0" eb="1">
+      <t>ミギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥</t>
+    <rPh sb="0" eb="1">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左奥</t>
+    <rPh sb="0" eb="1">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右奥</t>
+    <rPh sb="0" eb="2">
+      <t>ミギオク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>scenarioId</t>
+  </si>
+  <si>
+    <t>sceneId</t>
+  </si>
+  <si>
+    <t>scenarioName</t>
+  </si>
+  <si>
+    <t>春風とともに</t>
+    <rPh sb="0" eb="2">
+      <t>ハルカゼ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雲の向こうには青空が広がっている</t>
+    <rPh sb="0" eb="1">
+      <t>クモ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>アオゾラ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヒロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>きれいごとが一番</t>
+    <rPh sb="6" eb="8">
+      <t>イチバン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>scenarioId</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>eventOrder</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>command</t>
+  </si>
+  <si>
+    <t>arg1</t>
+  </si>
+  <si>
+    <t>arg2</t>
+  </si>
+  <si>
+    <t>arg3</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>voice</t>
+  </si>
+  <si>
+    <t>branchName</t>
+  </si>
+  <si>
+    <t>Character</t>
+  </si>
+  <si>
+    <t>CharacterOf</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bg</t>
+  </si>
+  <si>
+    <t>StartScenario</t>
+  </si>
+  <si>
+    <t>EndScenario</t>
+  </si>
+  <si>
+    <t>josei_04_a</t>
+  </si>
+  <si>
+    <t>赤マフ</t>
+    <rPh sb="0" eb="1">
+      <t>アカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>josei_06_a</t>
+  </si>
+  <si>
+    <t>josei_04_b</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>josei_04_c</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>josei_04_d</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セーラー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>josei_06_b</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>josei_06_c</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>josei_06_d</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セミロング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>josei_07_a</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>josei_07_b</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>josei_07_c</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>josei_07_d</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>aaaaa</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bbbbb</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ccccc</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ddddd</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あいうえお</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私の名前は</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>busitu_1</t>
+  </si>
+  <si>
+    <t>heya_1</t>
+  </si>
+  <si>
+    <t>kounai_1</t>
+  </si>
+  <si>
+    <t>rouka_1</t>
   </si>
 </sst>
 </file>
@@ -364,22 +650,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83201479-C5AF-401B-88B2-69A540A1652E}">
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="B6" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -389,21 +691,418 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9CF32D7-FF71-4897-BB7C-A7B7FD3214BF}">
-  <dimension ref="A1:D1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0560664E-5619-4E5A-9FCD-E2AD783289EA}">
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
         <v>0</v>
       </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>-200</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <f t="shared" ref="A4:A7" si="0">A3+1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>200</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>200</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>-200</v>
+      </c>
+      <c r="D6">
+        <v>200</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>200</v>
+      </c>
+      <c r="D7">
+        <v>200</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC5ECCD1-29FB-49AF-913A-43325B8D078F}">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="2" width="13.875" customWidth="1"/>
+    <col min="3" max="3" width="16.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2">
+        <v>300</v>
+      </c>
+      <c r="E2">
+        <v>300</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3">
+        <v>400</v>
+      </c>
+      <c r="E3">
+        <v>400</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <f t="shared" ref="A4:A13" si="0">A3+1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4">
+        <v>200</v>
+      </c>
+      <c r="E4">
+        <v>200</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5">
+        <v>1000</v>
+      </c>
+      <c r="E5">
+        <v>1000</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6">
+        <v>300</v>
+      </c>
+      <c r="E6">
+        <v>300</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7">
+        <v>400</v>
+      </c>
+      <c r="E7">
+        <v>400</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8">
+        <v>200</v>
+      </c>
+      <c r="E8">
+        <v>200</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9">
+        <v>1000</v>
+      </c>
+      <c r="E9">
+        <v>1000</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10">
+        <v>300</v>
+      </c>
+      <c r="E10">
+        <v>300</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11">
+        <v>400</v>
+      </c>
+      <c r="E11">
+        <v>400</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12">
+        <v>200</v>
+      </c>
+      <c r="E12">
+        <v>200</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13">
+        <v>1000</v>
+      </c>
+      <c r="E13">
+        <v>1000</v>
+      </c>
+      <c r="F13">
         <v>3</v>
       </c>
     </row>
@@ -413,23 +1112,498 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC5ECCD1-29FB-49AF-913A-43325B8D078F}">
-  <dimension ref="A1:D1"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="10.625" customWidth="1"/>
+    <col min="2" max="2" width="10.375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <f t="shared" ref="A4:A5" si="0">A3+1</f>
         <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>0.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{950537B1-565E-4765-914C-31B97E460F10}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="10.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9CF32D7-FF71-4897-BB7C-A7B7FD3214BF}">
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="9.875" customWidth="1"/>
+    <col min="2" max="2" width="10.625" customWidth="1"/>
+    <col min="3" max="3" width="12.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="G5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="G7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="G8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="G9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="G12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>2</v>
+      </c>
+      <c r="B27">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
+      <c r="C31" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/MasterData/ExcelFiles/testScenario.xlsx
+++ b/Assets/MasterData/ExcelFiles/testScenario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OGIX-PC046\source\repos\Unity6Test\Assets\MasterData\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D4D22B-5C11-4213-9B5D-B09AD4D05F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{949FA755-F23C-4CED-8F54-4CCF8DEA1BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="#guide" sheetId="5" r:id="rId1"/>
@@ -1321,6 +1321,9 @@
       <c r="C3" t="s">
         <v>37</v>
       </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4">
